--- a/data/atp/pairs_df.xlsx
+++ b/data/atp/pairs_df.xlsx
@@ -3850,10 +3850,19 @@
         <v>0</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
         <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31">
+        <v>18</v>
+      </c>
+      <c r="L31">
+        <v>9</v>
       </c>
       <c r="M31">
         <v>1</v>
@@ -4717,10 +4726,16 @@
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J55">
+        <v>3</v>
+      </c>
+      <c r="K55">
+        <v>5</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -4942,22 +4957,28 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>5</v>
+      </c>
+      <c r="K61">
+        <v>12</v>
       </c>
       <c r="M61">
         <v>3</v>
@@ -4980,19 +5001,25 @@
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J62">
+        <v>5</v>
+      </c>
+      <c r="K62">
+        <v>7</v>
       </c>
       <c r="M62">
         <v>1</v>
@@ -5094,10 +5121,16 @@
         <v>0</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
+      <c r="K65">
+        <v>9</v>
       </c>
       <c r="M65">
         <v>1</v>
@@ -5155,19 +5188,19 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -5439,7 +5472,13 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>8</v>
+      </c>
+      <c r="K74">
+        <v>2</v>
       </c>
       <c r="M74">
         <v>1</v>
@@ -5497,19 +5536,25 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J76">
+        <v>13</v>
+      </c>
+      <c r="K76">
+        <v>10</v>
       </c>
       <c r="M76">
         <v>2</v>
@@ -6385,7 +6430,16 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J100">
+        <v>5</v>
+      </c>
+      <c r="K100">
+        <v>10</v>
+      </c>
+      <c r="L100">
+        <v>9</v>
       </c>
       <c r="M100">
         <v>1</v>
@@ -6794,16 +6848,16 @@
         <v>0</v>
       </c>
       <c r="E111">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="F111">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="G111">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="H111">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -6847,10 +6901,10 @@
         <v>0</v>
       </c>
       <c r="H112">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -7172,19 +7226,19 @@
         <v>0</v>
       </c>
       <c r="E120">
-        <v>0.8148148148148148</v>
+        <v>1</v>
       </c>
       <c r="F120">
-        <v>0.8148148148148148</v>
+        <v>1</v>
       </c>
       <c r="G120">
-        <v>0.8148148148148148</v>
+        <v>1</v>
       </c>
       <c r="H120">
-        <v>0.8148148148148148</v>
+        <v>1</v>
       </c>
       <c r="I120">
-        <v>0.8148148148148148</v>
+        <v>1</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -8458,10 +8512,19 @@
         <v>0</v>
       </c>
       <c r="H151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151">
         <v>0</v>
+      </c>
+      <c r="J151">
+        <v>5</v>
+      </c>
+      <c r="K151">
+        <v>3</v>
+      </c>
+      <c r="L151">
+        <v>16</v>
       </c>
       <c r="M151">
         <v>1</v>
@@ -8493,10 +8556,16 @@
         <v>0</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J152">
+        <v>5</v>
+      </c>
+      <c r="K152">
+        <v>3</v>
       </c>
       <c r="M152">
         <v>1</v>
@@ -8563,7 +8632,7 @@
         <v>0</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
         <v>1</v>
@@ -8572,10 +8641,10 @@
         <v>3</v>
       </c>
       <c r="K154">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L154">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M154">
         <v>2</v>
@@ -8756,7 +8825,16 @@
         <v>0</v>
       </c>
       <c r="I159">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>11</v>
+      </c>
+      <c r="L159">
+        <v>4</v>
       </c>
       <c r="M159">
         <v>2</v>
@@ -8876,10 +8954,16 @@
         <v>0</v>
       </c>
       <c r="H162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>1</v>
       </c>
       <c r="M162">
         <v>1</v>
@@ -9586,10 +9670,16 @@
         <v>0</v>
       </c>
       <c r="H181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I181">
         <v>0</v>
+      </c>
+      <c r="J181">
+        <v>2</v>
+      </c>
+      <c r="K181">
+        <v>2</v>
       </c>
       <c r="M181">
         <v>1</v>
@@ -9665,9 +9755,15 @@
         <v>0</v>
       </c>
       <c r="H183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>8</v>
+      </c>
+      <c r="K183">
         <v>0</v>
       </c>
       <c r="M183">
@@ -10022,10 +10118,16 @@
         <v>0</v>
       </c>
       <c r="H192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I192">
         <v>0</v>
+      </c>
+      <c r="J192">
+        <v>11</v>
+      </c>
+      <c r="K192">
+        <v>16</v>
       </c>
       <c r="M192">
         <v>1</v>
@@ -10057,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="H193">
-        <v>0.6428571428571429</v>
+        <v>1</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -10294,19 +10396,28 @@
         <v>0</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199">
         <v>0</v>
       </c>
       <c r="I199">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J199">
+        <v>15</v>
+      </c>
+      <c r="K199">
+        <v>15</v>
+      </c>
+      <c r="L199">
+        <v>6</v>
       </c>
       <c r="M199">
         <v>1</v>
@@ -10332,16 +10443,25 @@
         <v>0</v>
       </c>
       <c r="F200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H200">
         <v>0</v>
       </c>
       <c r="I200">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>8</v>
+      </c>
+      <c r="K200">
+        <v>8</v>
+      </c>
+      <c r="L200">
+        <v>6</v>
       </c>
       <c r="M200">
         <v>2</v>
@@ -10443,9 +10563,15 @@
         <v>0</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>13</v>
+      </c>
+      <c r="K203">
         <v>0</v>
       </c>
       <c r="M203">
@@ -10478,10 +10604,16 @@
         <v>0</v>
       </c>
       <c r="H204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204">
         <v>0</v>
+      </c>
+      <c r="J204">
+        <v>18</v>
+      </c>
+      <c r="K204">
+        <v>2</v>
       </c>
       <c r="M204">
         <v>3</v>
@@ -10516,7 +10648,13 @@
         <v>0</v>
       </c>
       <c r="I205">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J205">
+        <v>5</v>
+      </c>
+      <c r="K205">
+        <v>8</v>
       </c>
       <c r="M205">
         <v>1</v>
@@ -10618,10 +10756,10 @@
         <v>0</v>
       </c>
       <c r="H208">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I208">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J208">
         <v>21</v>
@@ -10773,10 +10911,16 @@
         <v>0</v>
       </c>
       <c r="H212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I212">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>13</v>
+      </c>
+      <c r="K212">
+        <v>12</v>
       </c>
       <c r="M212">
         <v>1</v>
@@ -10878,19 +11022,25 @@
         <v>0</v>
       </c>
       <c r="E215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I215">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>8</v>
       </c>
       <c r="M215">
         <v>2</v>
@@ -11135,7 +11285,7 @@
         <v>0</v>
       </c>
       <c r="I222">
-        <v>0.9534883720930233</v>
+        <v>1</v>
       </c>
       <c r="J222">
         <v>11</v>
@@ -11707,30 +11857,21 @@
         <v>1</v>
       </c>
       <c r="D238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I238">
-        <v>1</v>
-      </c>
-      <c r="J238">
-        <v>0</v>
-      </c>
-      <c r="K238">
-        <v>0</v>
-      </c>
-      <c r="L238">
         <v>0</v>
       </c>
       <c r="M238">
@@ -11941,7 +12082,13 @@
         <v>0</v>
       </c>
       <c r="I244">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J244">
+        <v>5</v>
+      </c>
+      <c r="K244">
+        <v>10</v>
       </c>
       <c r="M244">
         <v>1</v>
@@ -11976,7 +12123,13 @@
         <v>0</v>
       </c>
       <c r="I245">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J245">
+        <v>3</v>
+      </c>
+      <c r="K245">
+        <v>14</v>
       </c>
       <c r="M245">
         <v>2</v>
@@ -12746,16 +12899,16 @@
         <v>0</v>
       </c>
       <c r="E267">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F267">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G267">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H267">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I267">
         <v>0</v>
@@ -12799,10 +12952,16 @@
         <v>0</v>
       </c>
       <c r="H268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I268">
         <v>0</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>7</v>
       </c>
       <c r="M268">
         <v>2</v>
@@ -12898,16 +13057,22 @@
         <v>0</v>
       </c>
       <c r="F271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H271">
         <v>0</v>
       </c>
       <c r="I271">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J271">
+        <v>3</v>
+      </c>
+      <c r="K271">
+        <v>11</v>
       </c>
       <c r="M271">
         <v>1</v>
@@ -12983,10 +13148,16 @@
         <v>0</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J273">
+        <v>8</v>
+      </c>
+      <c r="K273">
+        <v>6</v>
       </c>
       <c r="M273">
         <v>1</v>
@@ -13117,16 +13288,22 @@
         <v>0</v>
       </c>
       <c r="F277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H277">
         <v>0</v>
       </c>
       <c r="I277">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J277">
+        <v>8</v>
+      </c>
+      <c r="K277">
+        <v>3</v>
       </c>
       <c r="M277">
         <v>1</v>
@@ -13457,10 +13634,16 @@
         <v>0</v>
       </c>
       <c r="H285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I285">
         <v>0</v>
+      </c>
+      <c r="J285">
+        <v>10</v>
+      </c>
+      <c r="K285">
+        <v>22</v>
       </c>
       <c r="M285">
         <v>1</v>
@@ -13927,10 +14110,16 @@
         <v>0</v>
       </c>
       <c r="H298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I298">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J298">
+        <v>8</v>
+      </c>
+      <c r="K298">
+        <v>11</v>
       </c>
       <c r="M298">
         <v>1</v>
@@ -14140,19 +14329,19 @@
         <v>0</v>
       </c>
       <c r="E304">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="F304">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="G304">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="H304">
         <v>0</v>
       </c>
       <c r="I304">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="J304">
         <v>13</v>
@@ -14184,19 +14373,28 @@
         <v>0</v>
       </c>
       <c r="E305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I305">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J305">
+        <v>8</v>
+      </c>
+      <c r="K305">
+        <v>18</v>
+      </c>
+      <c r="L305">
+        <v>1</v>
       </c>
       <c r="M305">
         <v>1</v>
@@ -14494,19 +14692,25 @@
         <v>0</v>
       </c>
       <c r="E313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H313">
         <v>0</v>
       </c>
       <c r="I313">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J313">
+        <v>2</v>
+      </c>
+      <c r="K313">
+        <v>3</v>
       </c>
       <c r="M313">
         <v>2</v>
@@ -14947,16 +15151,22 @@
         <v>0</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G325">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H325">
         <v>0</v>
       </c>
       <c r="I325">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J325">
+        <v>5</v>
+      </c>
+      <c r="K325">
+        <v>1</v>
       </c>
       <c r="M325">
         <v>1</v>
@@ -15084,19 +15294,25 @@
         <v>0</v>
       </c>
       <c r="E329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H329">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I329">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J329">
+        <v>5</v>
+      </c>
+      <c r="K329">
+        <v>8</v>
       </c>
       <c r="M329">
         <v>2</v>
@@ -15268,10 +15484,16 @@
         <v>0</v>
       </c>
       <c r="H334">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I334">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J334">
+        <v>10</v>
+      </c>
+      <c r="K334">
+        <v>7</v>
       </c>
       <c r="M334">
         <v>2</v>
@@ -15391,9 +15613,18 @@
         <v>0</v>
       </c>
       <c r="H337">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I337">
+        <v>1</v>
+      </c>
+      <c r="J337">
+        <v>6</v>
+      </c>
+      <c r="K337">
+        <v>10</v>
+      </c>
+      <c r="L337">
         <v>0</v>
       </c>
       <c r="M337">
@@ -15864,19 +16095,25 @@
         <v>0</v>
       </c>
       <c r="E350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G350">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H350">
         <v>0</v>
       </c>
       <c r="I350">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J350">
+        <v>7</v>
+      </c>
+      <c r="K350">
+        <v>4</v>
       </c>
       <c r="M350">
         <v>5</v>
@@ -16004,16 +16241,16 @@
         <v>0</v>
       </c>
       <c r="E354">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="F354">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="G354">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="H354">
-        <v>0.9166666666666666</v>
+        <v>1</v>
       </c>
       <c r="I354">
         <v>0</v>
@@ -16089,16 +16326,16 @@
         <v>0</v>
       </c>
       <c r="E356">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="F356">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="G356">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="H356">
-        <v>0.7692307692307693</v>
+        <v>1</v>
       </c>
       <c r="I356">
         <v>0</v>
@@ -16142,10 +16379,10 @@
         <v>0</v>
       </c>
       <c r="H357">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I357">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J357">
         <v>15</v>
@@ -16177,16 +16414,16 @@
         <v>0</v>
       </c>
       <c r="E358">
-        <v>0.5666666666666667</v>
+        <v>1</v>
       </c>
       <c r="F358">
-        <v>0.5666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G358">
-        <v>0.5666666666666667</v>
+        <v>1</v>
       </c>
       <c r="H358">
-        <v>0.5666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I358">
         <v>0</v>
@@ -16779,13 +17016,13 @@
         <v>0</v>
       </c>
       <c r="E374">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="F374">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="G374">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="H374">
         <v>0</v>
@@ -16829,13 +17066,19 @@
         <v>0</v>
       </c>
       <c r="G375">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H375">
         <v>0</v>
       </c>
       <c r="I375">
         <v>0</v>
+      </c>
+      <c r="J375">
+        <v>13</v>
+      </c>
+      <c r="K375">
+        <v>2</v>
       </c>
       <c r="M375">
         <v>4</v>
@@ -16858,19 +17101,28 @@
         <v>0</v>
       </c>
       <c r="E376">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F376">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G376">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H376">
         <v>0</v>
       </c>
       <c r="I376">
         <v>0</v>
+      </c>
+      <c r="J376">
+        <v>0</v>
+      </c>
+      <c r="K376">
+        <v>10</v>
+      </c>
+      <c r="L376">
+        <v>12</v>
       </c>
       <c r="M376">
         <v>4</v>
@@ -16896,16 +17148,25 @@
         <v>0</v>
       </c>
       <c r="F377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G377">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H377">
         <v>0</v>
       </c>
       <c r="I377">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J377">
+        <v>8</v>
+      </c>
+      <c r="K377">
+        <v>10</v>
+      </c>
+      <c r="L377">
+        <v>7</v>
       </c>
       <c r="M377">
         <v>2</v>
@@ -17092,19 +17353,25 @@
         <v>0</v>
       </c>
       <c r="E382">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F382">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G382">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H382">
         <v>0</v>
       </c>
       <c r="I382">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J382">
+        <v>8</v>
+      </c>
+      <c r="K382">
+        <v>10</v>
       </c>
       <c r="M382">
         <v>1</v>
@@ -17583,19 +17850,25 @@
         <v>0</v>
       </c>
       <c r="E395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H395">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I395">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J395">
+        <v>6</v>
+      </c>
+      <c r="K395">
+        <v>12</v>
       </c>
       <c r="M395">
         <v>1</v>
@@ -17908,7 +18181,13 @@
         <v>0</v>
       </c>
       <c r="I403">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J403">
+        <v>18</v>
+      </c>
+      <c r="K403">
+        <v>14</v>
       </c>
       <c r="M403">
         <v>1</v>
@@ -17940,7 +18219,7 @@
         <v>0</v>
       </c>
       <c r="H404">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I404">
         <v>0</v>
@@ -18028,10 +18307,16 @@
         <v>0</v>
       </c>
       <c r="H406">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I406">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J406">
+        <v>0</v>
+      </c>
+      <c r="K406">
+        <v>6</v>
       </c>
       <c r="M406">
         <v>2</v>
@@ -18253,19 +18538,25 @@
         <v>0</v>
       </c>
       <c r="E412">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F412">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G412">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H412">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I412">
         <v>0</v>
+      </c>
+      <c r="J412">
+        <v>5</v>
+      </c>
+      <c r="K412">
+        <v>7</v>
       </c>
       <c r="M412">
         <v>1</v>
@@ -18580,16 +18871,25 @@
         <v>0</v>
       </c>
       <c r="F421">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G421">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H421">
         <v>0</v>
       </c>
       <c r="I421">
         <v>0</v>
+      </c>
+      <c r="J421">
+        <v>0</v>
+      </c>
+      <c r="K421">
+        <v>1</v>
+      </c>
+      <c r="L421">
+        <v>2</v>
       </c>
       <c r="M421">
         <v>1</v>
@@ -18650,16 +18950,22 @@
         <v>0</v>
       </c>
       <c r="F423">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G423">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H423">
         <v>0</v>
       </c>
       <c r="I423">
         <v>0</v>
+      </c>
+      <c r="J423">
+        <v>3</v>
+      </c>
+      <c r="K423">
+        <v>1</v>
       </c>
       <c r="M423">
         <v>2</v>
@@ -18945,16 +19251,16 @@
         <v>0</v>
       </c>
       <c r="E431">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="F431">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="G431">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="H431">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="I431">
         <v>0</v>
@@ -19109,7 +19415,7 @@
         <v>1</v>
       </c>
       <c r="D435">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E435">
         <v>0</v>
@@ -19118,13 +19424,19 @@
         <v>0</v>
       </c>
       <c r="G435">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H435">
         <v>0</v>
       </c>
       <c r="I435">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J435">
+        <v>25</v>
+      </c>
+      <c r="K435">
+        <v>26</v>
       </c>
       <c r="M435">
         <v>1</v>
@@ -19314,10 +19626,10 @@
         <v>0</v>
       </c>
       <c r="H440">
-        <v>0.8181818181818182</v>
+        <v>1</v>
       </c>
       <c r="I440">
-        <v>0.8181818181818182</v>
+        <v>1</v>
       </c>
       <c r="J440">
         <v>3</v>
@@ -19393,19 +19705,19 @@
         <v>0</v>
       </c>
       <c r="E442">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="F442">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="G442">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="H442">
         <v>0</v>
       </c>
       <c r="I442">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="J442">
         <v>10</v>
@@ -19783,19 +20095,25 @@
         <v>0</v>
       </c>
       <c r="E451">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F451">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G451">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H451">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I451">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J451">
+        <v>18</v>
+      </c>
+      <c r="K451">
+        <v>6</v>
       </c>
       <c r="M451">
         <v>3</v>
@@ -20769,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="E476">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="F476">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="G476">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="H476">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="I476">
-        <v>0.4285714285714285</v>
+        <v>1</v>
       </c>
       <c r="J476">
         <v>6</v>
@@ -20813,19 +21131,28 @@
         <v>0</v>
       </c>
       <c r="E477">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F477">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G477">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H477">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I477">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J477">
+        <v>17</v>
+      </c>
+      <c r="K477">
+        <v>20</v>
+      </c>
+      <c r="L477">
+        <v>4</v>
       </c>
       <c r="M477">
         <v>2</v>
@@ -20895,16 +21222,22 @@
         <v>0</v>
       </c>
       <c r="F479">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G479">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H479">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I479">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J479">
+        <v>8</v>
+      </c>
+      <c r="K479">
+        <v>6</v>
       </c>
       <c r="M479">
         <v>1</v>
@@ -20927,19 +21260,28 @@
         <v>0</v>
       </c>
       <c r="E480">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F480">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G480">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H480">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I480">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J480">
+        <v>3</v>
+      </c>
+      <c r="K480">
+        <v>2</v>
+      </c>
+      <c r="L480">
+        <v>1</v>
       </c>
       <c r="M480">
         <v>3</v>
@@ -21050,16 +21392,22 @@
         <v>0</v>
       </c>
       <c r="F483">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G483">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H483">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I483">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J483">
+        <v>3</v>
+      </c>
+      <c r="K483">
+        <v>1</v>
       </c>
       <c r="M483">
         <v>2</v>
@@ -21685,10 +22033,16 @@
         <v>0</v>
       </c>
       <c r="H499">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I499">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J499">
+        <v>0</v>
+      </c>
+      <c r="K499">
+        <v>8</v>
       </c>
       <c r="M499">
         <v>1</v>
@@ -21790,19 +22144,19 @@
         <v>0</v>
       </c>
       <c r="E502">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="F502">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="G502">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="H502">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="I502">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="J502">
         <v>0</v>
@@ -22071,19 +22425,19 @@
         <v>0</v>
       </c>
       <c r="E509">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F509">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G509">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H509">
         <v>0</v>
       </c>
       <c r="I509">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J509">
         <v>7</v>
@@ -22419,7 +22773,7 @@
         <v>0</v>
       </c>
       <c r="H518">
-        <v>0.9090909090909091</v>
+        <v>1</v>
       </c>
       <c r="I518">
         <v>0</v>
@@ -22457,16 +22811,22 @@
         <v>0</v>
       </c>
       <c r="F519">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G519">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H519">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I519">
         <v>0</v>
+      </c>
+      <c r="J519">
+        <v>8</v>
+      </c>
+      <c r="K519">
+        <v>16</v>
       </c>
       <c r="M519">
         <v>4</v>
@@ -23094,19 +23454,19 @@
         <v>0</v>
       </c>
       <c r="E536">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="F536">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="G536">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="H536">
         <v>0</v>
       </c>
       <c r="I536">
-        <v>0.375</v>
+        <v>1</v>
       </c>
       <c r="J536">
         <v>0</v>
@@ -23270,10 +23630,19 @@
         <v>0</v>
       </c>
       <c r="H540">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I540">
         <v>0</v>
+      </c>
+      <c r="J540">
+        <v>10</v>
+      </c>
+      <c r="K540">
+        <v>12</v>
+      </c>
+      <c r="L540">
+        <v>7</v>
       </c>
       <c r="M540">
         <v>3</v>
@@ -23454,7 +23823,7 @@
         <v>1</v>
       </c>
       <c r="H545">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I545">
         <v>1</v>
@@ -23463,7 +23832,7 @@
         <v>0</v>
       </c>
       <c r="K545">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="M545">
         <v>3</v>
@@ -23615,7 +23984,13 @@
         <v>0</v>
       </c>
       <c r="I549">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J549">
+        <v>8</v>
+      </c>
+      <c r="K549">
+        <v>6</v>
       </c>
       <c r="M549">
         <v>4</v>
@@ -23638,13 +24013,13 @@
         <v>0</v>
       </c>
       <c r="E550">
-        <v>0.9259259259259259</v>
+        <v>1</v>
       </c>
       <c r="F550">
-        <v>0.9259259259259259</v>
+        <v>1</v>
       </c>
       <c r="G550">
-        <v>0.9259259259259259</v>
+        <v>1</v>
       </c>
       <c r="H550">
         <v>0</v>
@@ -23854,22 +24229,22 @@
         <v>18</v>
       </c>
       <c r="D556">
-        <v>0.927536231884058</v>
+        <v>1</v>
       </c>
       <c r="E556">
-        <v>0.927536231884058</v>
+        <v>1</v>
       </c>
       <c r="F556">
-        <v>0.927536231884058</v>
+        <v>1</v>
       </c>
       <c r="G556">
-        <v>0.927536231884058</v>
+        <v>1</v>
       </c>
       <c r="H556">
-        <v>0.927536231884058</v>
+        <v>1</v>
       </c>
       <c r="I556">
-        <v>0.927536231884058</v>
+        <v>1</v>
       </c>
       <c r="J556">
         <v>8</v>
@@ -24126,19 +24501,16 @@
         <v>0</v>
       </c>
       <c r="H563">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I563">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J563">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K563">
-        <v>8</v>
-      </c>
-      <c r="L563">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M563">
         <v>1</v>
@@ -24261,7 +24633,13 @@
         <v>0</v>
       </c>
       <c r="I566">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J566">
+        <v>0</v>
+      </c>
+      <c r="K566">
+        <v>1</v>
       </c>
       <c r="M566">
         <v>3</v>
@@ -25424,10 +25802,16 @@
         <v>0</v>
       </c>
       <c r="H597">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I597">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J597">
+        <v>7</v>
+      </c>
+      <c r="K597">
+        <v>13</v>
       </c>
       <c r="M597">
         <v>2</v>
@@ -25538,10 +25922,19 @@
         <v>0</v>
       </c>
       <c r="H600">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I600">
         <v>0</v>
+      </c>
+      <c r="J600">
+        <v>6</v>
+      </c>
+      <c r="K600">
+        <v>13</v>
+      </c>
+      <c r="L600">
+        <v>11</v>
       </c>
       <c r="M600">
         <v>1</v>
@@ -25564,19 +25957,28 @@
         <v>0</v>
       </c>
       <c r="E601">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F601">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G601">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H601">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I601">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J601">
+        <v>13</v>
+      </c>
+      <c r="K601">
+        <v>13</v>
+      </c>
+      <c r="L601">
+        <v>11</v>
       </c>
       <c r="M601">
         <v>2</v>
@@ -25728,19 +26130,19 @@
         <v>0</v>
       </c>
       <c r="E605">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="F605">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G605">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H605">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="I605">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="J605">
         <v>3</v>
@@ -25842,19 +26244,25 @@
         <v>0</v>
       </c>
       <c r="E608">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F608">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G608">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H608">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I608">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J608">
+        <v>33</v>
+      </c>
+      <c r="K608">
+        <v>29</v>
       </c>
       <c r="M608">
         <v>1</v>
@@ -25886,10 +26294,16 @@
         <v>0</v>
       </c>
       <c r="H609">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I609">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J609">
+        <v>13</v>
+      </c>
+      <c r="K609">
+        <v>4</v>
       </c>
       <c r="M609">
         <v>1</v>
@@ -26061,10 +26475,10 @@
         <v>0</v>
       </c>
       <c r="H614">
-        <v>0.3076923076923077</v>
+        <v>1</v>
       </c>
       <c r="I614">
-        <v>0.3076923076923077</v>
+        <v>1</v>
       </c>
       <c r="J614">
         <v>10</v>
@@ -26096,19 +26510,28 @@
         <v>0</v>
       </c>
       <c r="E615">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F615">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G615">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H615">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I615">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J615">
+        <v>10</v>
+      </c>
+      <c r="K615">
+        <v>12</v>
+      </c>
+      <c r="L615">
+        <v>2</v>
       </c>
       <c r="M615">
         <v>2</v>
@@ -26184,19 +26607,16 @@
         <v>1</v>
       </c>
       <c r="H617">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I617">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J617">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K617">
-        <v>10</v>
-      </c>
-      <c r="L617">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M617">
         <v>1</v>
@@ -27667,19 +28087,19 @@
         <v>0</v>
       </c>
       <c r="E655">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F655">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G655">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H655">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I655">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J655">
         <v>10</v>
@@ -27799,10 +28219,16 @@
         <v>0</v>
       </c>
       <c r="H658">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I658">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J658">
+        <v>3</v>
+      </c>
+      <c r="K658">
+        <v>10</v>
       </c>
       <c r="M658">
         <v>1</v>
@@ -28115,19 +28541,19 @@
         <v>0</v>
       </c>
       <c r="E666">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F666">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G666">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="H666">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I666">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J666">
         <v>5</v>
@@ -28370,16 +28796,16 @@
         <v>0</v>
       </c>
       <c r="F672">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="G672">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="H672">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="I672">
-        <v>0.7142857142857143</v>
+        <v>1</v>
       </c>
       <c r="J672">
         <v>28</v>
@@ -28950,7 +29376,16 @@
         <v>0</v>
       </c>
       <c r="I686">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J686">
+        <v>13</v>
+      </c>
+      <c r="K686">
+        <v>12</v>
+      </c>
+      <c r="L686">
+        <v>1</v>
       </c>
       <c r="M686">
         <v>2</v>
@@ -28985,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="I687">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J687">
         <v>8</v>
@@ -29087,19 +29522,28 @@
         <v>0</v>
       </c>
       <c r="E690">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F690">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G690">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H690">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I690">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J690">
+        <v>8</v>
+      </c>
+      <c r="K690">
+        <v>2</v>
+      </c>
+      <c r="L690">
+        <v>1</v>
       </c>
       <c r="M690">
         <v>3</v>
@@ -29271,19 +29715,19 @@
         <v>0</v>
       </c>
       <c r="E695">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="F695">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="G695">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="H695">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="I695">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="J695">
         <v>0</v>
@@ -29359,16 +29803,16 @@
         <v>0</v>
       </c>
       <c r="E697">
-        <v>0.9024390243902439</v>
+        <v>1</v>
       </c>
       <c r="F697">
-        <v>0.9024390243902439</v>
+        <v>1</v>
       </c>
       <c r="G697">
-        <v>0.9024390243902439</v>
+        <v>1</v>
       </c>
       <c r="H697">
-        <v>0.9024390243902439</v>
+        <v>1</v>
       </c>
       <c r="I697">
         <v>0</v>
@@ -29848,19 +30292,19 @@
         <v>0</v>
       </c>
       <c r="E709">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="F709">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="G709">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H709">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="I709">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J709">
         <v>5</v>
@@ -29901,10 +30345,19 @@
         <v>0</v>
       </c>
       <c r="H710">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I710">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J710">
+        <v>13</v>
+      </c>
+      <c r="K710">
+        <v>10</v>
+      </c>
+      <c r="L710">
+        <v>1</v>
       </c>
       <c r="M710">
         <v>1</v>
@@ -29933,13 +30386,22 @@
         <v>0</v>
       </c>
       <c r="G711">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H711">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I711">
         <v>0</v>
+      </c>
+      <c r="J711">
+        <v>8</v>
+      </c>
+      <c r="K711">
+        <v>8</v>
+      </c>
+      <c r="L711">
+        <v>8</v>
       </c>
       <c r="M711">
         <v>1</v>
@@ -30099,30 +30561,21 @@
         <v>7</v>
       </c>
       <c r="D716">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="E716">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="F716">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="G716">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="H716">
-        <v>0.4444444444444444</v>
+        <v>0</v>
       </c>
       <c r="I716">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="J716">
-        <v>0</v>
-      </c>
-      <c r="K716">
-        <v>0</v>
-      </c>
-      <c r="L716">
         <v>0</v>
       </c>
       <c r="M716">
@@ -30533,10 +30986,19 @@
         <v>0</v>
       </c>
       <c r="H726">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I726">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J726">
+        <v>13</v>
+      </c>
+      <c r="K726">
+        <v>6</v>
+      </c>
+      <c r="L726">
+        <v>3</v>
       </c>
       <c r="M726">
         <v>2</v>
@@ -30802,19 +31264,19 @@
         <v>0</v>
       </c>
       <c r="E733">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="F733">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="G733">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="H733">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="I733">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="J733">
         <v>13</v>
@@ -30925,19 +31387,19 @@
         <v>0</v>
       </c>
       <c r="E736">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F736">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G736">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="H736">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="I736">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J736">
         <v>10</v>
@@ -31001,22 +31463,22 @@
         <v>2</v>
       </c>
       <c r="D738">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E738">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F738">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G738">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H738">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I738">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J738">
         <v>0</v>
@@ -31057,10 +31519,16 @@
         <v>0</v>
       </c>
       <c r="H739">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I739">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J739">
+        <v>18</v>
+      </c>
+      <c r="K739">
+        <v>18</v>
       </c>
       <c r="M739">
         <v>1</v>
@@ -31153,18 +31621,24 @@
         <v>0</v>
       </c>
       <c r="E742">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F742">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G742">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H742">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I742">
+        <v>1</v>
+      </c>
+      <c r="J742">
+        <v>0</v>
+      </c>
+      <c r="K742">
         <v>0</v>
       </c>
       <c r="M742">
@@ -31270,7 +31744,13 @@
         <v>0</v>
       </c>
       <c r="I745">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="J745">
+        <v>8</v>
+      </c>
+      <c r="K745">
+        <v>5</v>
       </c>
       <c r="M745">
         <v>1</v>

--- a/data/atp/pairs_df.xlsx
+++ b/data/atp/pairs_df.xlsx
@@ -2300,16 +2300,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2325,7 +2317,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2333,30 +2325,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2655,46 +2629,46 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
     </row>
